--- a/data/trans_bre/IP07_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -0,49</t>
+          <t>-6,0; -0,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,0</t>
+          <t>-4,65; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 4,2</t>
+          <t>-2,8; 5,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,87</t>
+          <t>-3,99; 3,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,31</t>
+          <t>-2,86; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,88</t>
+          <t>-3,95; 0,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 5,18</t>
+          <t>-4,54; 4,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,75</t>
+          <t>-6,6; 0,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 7,62</t>
+          <t>-2,13; 7,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,0</t>
+          <t>-8,49; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>-8,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,73</t>
+          <t>-2,8; 1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,71</t>
+          <t>-4,1; 1,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,61</t>
+          <t>-3,68; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 11,68</t>
+          <t>-2,52; 2,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,5; 200,87</t>
+          <t>-82,35; 203,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,62; 62,73</t>
+          <t>-70,92; 78,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 124,43</t>
+          <t>-80,12; 118,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 1069,8</t>
+          <t>-76,86; 231,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 1,48</t>
+          <t>-6,19; 1,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,31</t>
+          <t>-2,22; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,69</t>
+          <t>-1,43; 5,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,99</t>
+          <t>-2,66; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-88,23; 80,47</t>
+          <t>-89,35; 73,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 437,25</t>
+          <t>-76,68; 402,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 446,66</t>
+          <t>-49,34; 611,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,62; 433,67</t>
+          <t>-76,09; 580,78</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -1,07</t>
+          <t>-10,48; -0,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 10,47</t>
+          <t>-2,21; 10,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,12</t>
+          <t>-1,89; 5,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 6,31</t>
+          <t>-3,88; 6,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,6</t>
+          <t>-3,32; -0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,66</t>
+          <t>-1,07; 1,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,3</t>
+          <t>-1,28; 1,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,87</t>
+          <t>-1,43; 1,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-76,94; -17,58</t>
+          <t>-76,26; -18,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 101,22</t>
+          <t>-37,96; 97,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 91,6</t>
+          <t>-48,3; 96,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 192,31</t>
+          <t>-46,02; 91,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,169 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-84,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.320273977105852</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.886037982296603</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.295997173195127</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.8794726413643036</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.8439124190013324</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.5010584516420232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; -0,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,66</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 5,02</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.995993520028583</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.649895172571176</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.804881566021376</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.231912459172043</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.66054592145302</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.016319762283671</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-5,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-14,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-64,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 3,34</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 2,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,95; 0,79</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,54; 4,96</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.144056890132176</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1940336516408392</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.166620697138505</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.3144485670080955</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.05735559021213608</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1449589638588247</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.643744216403021</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1051962974964184</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,53</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-72,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>105,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.991895736396331</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.864059330735492</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.951679588243583</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.542944722039272</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,6; 0,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,36</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 7,2</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,49; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.341743842222602</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.162172100162062</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.791714087617826</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.9613721756385</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +789,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-28,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-27,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-34,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,11%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.439432775115879</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.492622018520164</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.752672327403697</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.526243878182181</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.7254454040556229</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.050477111463416</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 1,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,1; 1,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 1,35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 2,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-82,35; 203,88</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-70,92; 78,93</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-80,12; 118,31</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-76,86; 231,95</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.599264022888214</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.130890048102492</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.488805577117569</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7086863865501215</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.360253974670422</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.19789027394829</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-48,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>58,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 1,28</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 3,8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 5,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 4,03</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-89,35; 73,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-76,68; 402,47</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-49,34; 611,43</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-76,09; 580,78</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.6705414941604652</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.15697253881088</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.017213312020048</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.2072283163860603</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.284339195674557</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2734576776818334</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3482308037386231</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08108542512267947</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-4,6</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-85,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>113,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>107,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29,84%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.803660782823251</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.096843866342657</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.684064943589544</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.516703772066578</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8235126160754623</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7091921813686504</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8011735058918338</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7685950939697948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-10,48; -0,88</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 10,3</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-1,89; 5,15</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-3,88; 6,74</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.62267516387189</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.798429217499129</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.352073865281421</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.489291355983227</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.038832085896409</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7893221078402366</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.183112615858062</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.319500834334336</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +975,281 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-54,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-2.27723396366456</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5945126900894139</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.399380554032199</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.2868666724115312</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.4817591432420085</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2697484455343476</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.5863895227047518</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.1216881422466055</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; -0,61</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 1,61</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 1,28</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 1,76</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-76,26; -18,54</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-37,96; 97,97</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-48,3; 96,84</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-46,02; 91,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.188619869924209</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.223661179155195</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.431708334936225</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.656374376986948</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8935013220518088</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.766755454820379</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4934270638386445</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.7608828882658765</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.278919926757236</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.797212966568825</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.393184086739373</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.025561058009566</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7321213127680001</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>4.024681275731746</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>6.114256140699503</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>5.807759664099595</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-4.6048890930897</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.962550782875137</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.049226940132415</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.9408685552717948</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.8544634538607884</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.138311024987808</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.07811600441165</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.2984082207875837</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-10.47953414714054</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-2.208587125901628</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-1.890254570688891</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-3.876724212495745</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-0.8767297325635829</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>10.29874524746656</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.151601231765151</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.741322928489152</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.828754112199947</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.228660463182671</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.08264138637890037</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.1112347421899283</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.5472760183096195</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.102599963914433</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03951020360633859</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.04476388915881515</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.315350136340191</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.071623542328529</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.275418374379354</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.431431433937622</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.7625793978061332</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.3796399273005308</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4830470744583139</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.4602201289597022</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-0.6100366940620865</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.608033710350077</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.277300503968394</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.759681176778155</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-0.1854229118686285</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.9796614110342019</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.9683604218130056</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.9135797918480824</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1257,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
